--- a/data/trans_camb/IQ2605_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IQ2605_R2-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30,85</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21,87</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>24,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18,24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,85</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,29</t>
+          <t>17,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,77</t>
+          <t>19,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 23,24</t>
+          <t>6,5; 29,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,05; 34,53</t>
+          <t>20,61; 41,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 32,09</t>
+          <t>6,22; 36,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 29,82</t>
+          <t>-0,21; 22,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 39,96</t>
+          <t>13,47; 34,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 35,63</t>
+          <t>0,63; 31,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 22,74</t>
+          <t>6,4; 22,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,18; 35,62</t>
+          <t>19,9; 35,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 29,32</t>
+          <t>7,31; 30,07</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>57,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40,81%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>20,87%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>44,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34,6%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 47,48</t>
+          <t>11,24; 63,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,62; 71,76</t>
+          <t>34,23; 88,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 63,25</t>
+          <t>11,05; 75,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 63,65</t>
+          <t>-0,33; 44,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,83; 86,04</t>
+          <t>22,68; 70,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 74,44</t>
+          <t>1,96; 63,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 45,37</t>
+          <t>11,59; 45,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 72,19</t>
+          <t>33,78; 70,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 57,61</t>
+          <t>13,0; 58,43</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25,95</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,74</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>16,4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>17,53</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,78</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,95</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,2</t>
+          <t>12,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 27,52</t>
+          <t>-6,74; 16,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 27,74</t>
+          <t>16,28; 36,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 24,73</t>
+          <t>-7,13; 30,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 17,19</t>
+          <t>5,61; 28,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,05; 36,36</t>
+          <t>6,75; 28,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 28,87</t>
+          <t>-5,59; 26,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 19,46</t>
+          <t>2,99; 18,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 30,06</t>
+          <t>14,44; 28,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 22,49</t>
+          <t>-0,57; 25,04</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43,18%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21,2%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>26,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>28,71%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,18%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 52,24</t>
+          <t>-9,81; 32,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 52,43</t>
+          <t>23,95; 69,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 43,39</t>
+          <t>-11,71; 54,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 31,5</t>
+          <t>8,16; 51,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,92; 69,91</t>
+          <t>10,54; 53,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 53,57</t>
+          <t>-8,22; 47,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 35,73</t>
+          <t>4,88; 32,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,69; 54,05</t>
+          <t>21,96; 52,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 38,8</t>
+          <t>-0,14; 45,46</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18,27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,89</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>20,8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>16,78</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18,27</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,89</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>5,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 34,48</t>
+          <t>6,51; 29,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 29,81</t>
+          <t>9,7; 32,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 26,22</t>
+          <t>-15,05; 26,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 28,97</t>
+          <t>8,46; 33,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 33,36</t>
+          <t>3,03; 29,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 28,29</t>
+          <t>-27,53; 26,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,66</t>
+          <t>11,7; 27,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 28,76</t>
+          <t>10,53; 28,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 21,05</t>
+          <t>-12,58; 20,88</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33,12%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>39,18%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>31,62%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,67%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41,51%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,12; 77,37</t>
+          <t>10,83; 60,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 63,37</t>
+          <t>16,86; 66,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 55,69</t>
+          <t>-25,19; 51,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,53; 59,22</t>
+          <t>13,92; 75,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,93; 68,34</t>
+          <t>5,7; 64,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 54,93</t>
+          <t>-47,16; 55,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,93; 56,6</t>
+          <t>19,37; 56,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,17; 58,67</t>
+          <t>17,34; 56,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 42,3</t>
+          <t>-21,15; 40,86</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26,13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32,18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>15,3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>16,47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,67</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27,3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26,13</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,26</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22,21</t>
+          <t>21,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 23,29</t>
+          <t>20,02; 34,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,92; 24,46</t>
+          <t>18,71; 33,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 24,36</t>
+          <t>19,19; 42,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,29; 34,57</t>
+          <t>7,51; 22,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,04; 33,25</t>
+          <t>10,03; 24,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,29; 42,65</t>
+          <t>-5,08; 22,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,14; 26,69</t>
+          <t>16,4; 26,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,31; 26,54</t>
+          <t>15,83; 26,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,68; 30,47</t>
+          <t>12,17; 29,99</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>52,5%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>50,25%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>61,87%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>26,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>27,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>52,5%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>50,25%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,55; 43,37</t>
+          <t>34,46; 73,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,07; 45,36</t>
+          <t>33,75; 70,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 43,24</t>
+          <t>36,37; 89,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34,62; 74,85</t>
+          <t>12,15; 41,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,77; 71,26</t>
+          <t>16,14; 45,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,97; 88,76</t>
+          <t>-8,39; 39,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,82; 51,01</t>
+          <t>28,39; 52,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,95; 51,19</t>
+          <t>26,65; 51,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,22; 56,8</t>
+          <t>21,48; 56,11</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18,65</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29,53</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31,05</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>21,33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>25,75</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>31,74</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18,65</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>29,53</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,97</t>
+          <t>29,81</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>31,88</t>
+          <t>30,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,57; 31,61</t>
+          <t>9,08; 27,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,5; 35,71</t>
+          <t>20,68; 39,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,18; 44,46</t>
+          <t>16,95; 43,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,92; 28,92</t>
+          <t>10,78; 30,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,68; 38,7</t>
+          <t>15,93; 35,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,64; 43,26</t>
+          <t>9,1; 44,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,75; 27,22</t>
+          <t>13,33; 27,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,96; 34,23</t>
+          <t>20,44; 33,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,67; 41,23</t>
+          <t>20,13; 40,2</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>37,02%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>58,62%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>61,65%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>42,23%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>50,98%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>62,83%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>58,62%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19,91; 72,26</t>
+          <t>16,26; 61,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>27,79; 83,83</t>
+          <t>36,79; 88,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26,22; 99,3</t>
+          <t>31,45; 97,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,11; 63,68</t>
+          <t>18,48; 70,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>36,89; 86,95</t>
+          <t>27,95; 83,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,77; 96,37</t>
+          <t>17,9; 96,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,75; 59,37</t>
+          <t>24,51; 58,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>37,79; 72,88</t>
+          <t>37,65; 74,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41,09; 88,35</t>
+          <t>38,91; 87,31</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>31,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18,64</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>25,5</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>36,01</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>31,86</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>31,83</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>31,0</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>18,64</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,24</t>
+          <t>30,89</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29,74</t>
+          <t>28,28</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>23,24; 49,74</t>
+          <t>18,08; 44,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17,57; 43,75</t>
+          <t>6,06; 32,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,49; 51,04</t>
+          <t>4,7; 43,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19,04; 43,84</t>
+          <t>22,75; 48,71</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,81; 31,62</t>
+          <t>17,83; 43,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,93; 43,38</t>
+          <t>0,46; 51,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,71; 43,24</t>
+          <t>25,47; 42,6</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14,72; 33,9</t>
+          <t>16,76; 34,98</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,2; 42,51</t>
+          <t>11,75; 42,36</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>68,07%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>55,99%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>89,73%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>79,4%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>79,32%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>68,07%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>40,94%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49,4; 157,75</t>
+          <t>34,35; 120,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38,06; 134,46</t>
+          <t>11,48; 87,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9,06; 151,16</t>
+          <t>10,51; 115,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35,86; 119,25</t>
+          <t>49,29; 147,23</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,96; 85,9</t>
+          <t>36,72; 127,53</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,34; 112,34</t>
+          <t>2,56; 145,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,79; 116,3</t>
+          <t>52,79; 116,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>31,81; 92,72</t>
+          <t>34,44; 92,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31,45; 113,78</t>
+          <t>26,44; 110,2</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>20,79</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>26,51</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>24,29</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>18,88</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>21,38</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>17,33</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>20,79</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>26,51</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,33</t>
+          <t>16,6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,25</t>
+          <t>20,85</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,91</t>
+          <t>16,7; 24,82</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17,22; 25,42</t>
+          <t>22,31; 29,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,44; 24,16</t>
+          <t>17,57; 30,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16,86; 24,65</t>
+          <t>14,7; 23,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,92; 30,62</t>
+          <t>17,08; 25,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,54; 30,68</t>
+          <t>9,23; 23,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,14; 22,76</t>
+          <t>16,88; 22,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>21,09; 26,76</t>
+          <t>21,4; 27,02</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16,32; 25,58</t>
+          <t>15,57; 25,44</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>50,25%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>46,03%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>34,65%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>39,23%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>31,81%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>39,4%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>50,25%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>25,86; 43,93</t>
+          <t>30,21; 49,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>30,36; 48,88</t>
+          <t>39,88; 59,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16,65; 45,22</t>
+          <t>32,32; 58,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30,56; 48,68</t>
+          <t>25,7; 44,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>41,44; 61,45</t>
+          <t>30,02; 48,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,22; 59,95</t>
+          <t>16,63; 44,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,06; 43,6</t>
+          <t>30,46; 43,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>38,38; 51,48</t>
+          <t>38,42; 52,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>29,98; 48,67</t>
+          <t>28,22; 48,42</t>
         </is>
       </c>
     </row>
